--- a/docs/bikefit_questionnaire.xlsx
+++ b/docs/bikefit_questionnaire.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ringo\opt\tsugie\faceman2\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6838F2-6C74-4DEB-8FC0-DF6AE4EA15AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C626BBFF-1953-4850-BFE0-D5A49BB8FB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6700" yWindow="21490" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7770" yWindow="4960" windowWidth="28800" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
@@ -9760,63 +9760,63 @@
         <v>50</v>
       </c>
       <c r="R17">
-        <f t="shared" ref="R17:R62" si="2">B17*10</f>
+        <f t="shared" ref="R17:R47" si="2">B17*10</f>
         <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" ref="S17:S62" si="3">C17*10</f>
+        <f t="shared" ref="S17:S47" si="3">C17*10</f>
         <v>0</v>
       </c>
       <c r="T17">
-        <f t="shared" ref="T17:T62" si="4">D17*10</f>
+        <f t="shared" ref="T17:T47" si="4">D17*10</f>
         <v>0</v>
       </c>
       <c r="U17">
-        <f t="shared" ref="U17:U62" si="5">E17*10</f>
+        <f t="shared" ref="U17:U47" si="5">E17*10</f>
         <v>0</v>
       </c>
       <c r="V17">
-        <f t="shared" ref="V17:V62" si="6">F17*10</f>
+        <f t="shared" ref="V17:V47" si="6">F17*10</f>
         <v>0</v>
       </c>
       <c r="W17">
-        <f t="shared" ref="W17:W62" si="7">G17*10</f>
+        <f t="shared" ref="W17:W47" si="7">G17*10</f>
         <v>0</v>
       </c>
       <c r="X17">
-        <f t="shared" ref="X17:X62" si="8">H17*10</f>
+        <f t="shared" ref="X17:X47" si="8">H17*10</f>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f t="shared" ref="Y17:Y62" si="9">I17*10</f>
+        <f t="shared" ref="Y17:Y47" si="9">I17*10</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f t="shared" ref="Z17:Z62" si="10">J17*10</f>
+        <f t="shared" ref="Z17:Z47" si="10">J17*10</f>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f t="shared" ref="AA17:AA62" si="11">K17*10</f>
+        <f t="shared" ref="AA17:AA47" si="11">K17*10</f>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f t="shared" ref="AB17:AB62" si="12">L17*10</f>
+        <f t="shared" ref="AB17:AB47" si="12">L17*10</f>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" ref="AC17:AC62" si="13">M17*10</f>
+        <f t="shared" ref="AC17:AC47" si="13">M17*10</f>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f t="shared" ref="AD17:AD62" si="14">N17*10</f>
+        <f t="shared" ref="AD17:AD47" si="14">N17*10</f>
         <v>50</v>
       </c>
       <c r="AE17">
-        <f t="shared" ref="AE17:AE62" si="15">O17*10</f>
+        <f t="shared" ref="AE17:AE47" si="15">O17*10</f>
         <v>50</v>
       </c>
       <c r="AF17">
-        <f t="shared" ref="AF17:AF62" si="16">P17*10</f>
+        <f t="shared" ref="AF17:AF47" si="16">P17*10</f>
         <v>0</v>
       </c>
     </row>
